--- a/templates/excel-templates/MBAA_Results.xlsx
+++ b/templates/excel-templates/MBAA_Results.xlsx
@@ -84,7 +84,7 @@
     <t>mbaa_results</t>
   </si>
   <si>
-    <t>Schema Version 3.34</t>
+    <t>Schema Version 3.35</t>
   </si>
   <si>
     <t>Please do not delete or edit this column</t>

--- a/templates/excel-templates/MBAA_Results.xlsx
+++ b/templates/excel-templates/MBAA_Results.xlsx
@@ -84,7 +84,7 @@
     <t>mbaa_results</t>
   </si>
   <si>
-    <t>Schema Version 3.35</t>
+    <t>Schema Version 3.36</t>
   </si>
   <si>
     <t>Please do not delete or edit this column</t>
